--- a/boring_stuff/sampleChart.xlsx
+++ b/boring_stuff/sampleChart.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <s:workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <s:bookViews>
-    <s:workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
-  </s:bookViews>
-  <s:sheets>
-    <s:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" r:id="rId1"/>
-  </s:sheets>
-  <s:definedNames/>
-  <s:calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
-</s:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="0"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23,16 +19,16 @@
   <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,154 +44,183 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <c:lang val="en-GB"/>
-  <c:chart>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.113333333333333"/>
-          <c:y val="0.22"/>
-          <c:w val="0.6"/>
-          <c:h val="0.6"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>First series</c:v>
-          </c:tx>
-          <c:val>
-            <c:numRef>
-              <c:f>'Sheet'!$A$1:$A$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:axId val="60871424"/>
-        <c:axId val="60873344"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="60871424"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:axPos val="b"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="60873344"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="60873344"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="12.0"/>
-          <c:min val="0.0"/>
-        </c:scaling>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="60871424"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="2.0"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" footer="0.3" header="0.3" l="0.7" r="0.7" t="0.75"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>My chart</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Sheet'!$A$1:$A$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="952500" y="476250"/>
-    <xdr:ext cx="2857500" cy="1905000"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
-        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -482,65 +507,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row spans="1:1" r="1">
+    <row r="1">
       <c r="A1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row spans="1:1" r="2">
+    <row r="2">
       <c r="A2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row spans="1:1" r="3">
+    <row r="3">
       <c r="A3" t="n">
         <v>3</v>
       </c>
     </row>
-    <row spans="1:1" r="4">
+    <row r="4">
       <c r="A4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row spans="1:1" r="5">
+    <row r="5">
       <c r="A5" t="n">
         <v>5</v>
       </c>
     </row>
-    <row spans="1:1" r="6">
+    <row r="6">
       <c r="A6" t="n">
         <v>6</v>
       </c>
     </row>
-    <row spans="1:1" r="7">
+    <row r="7">
       <c r="A7" t="n">
         <v>7</v>
       </c>
     </row>
-    <row spans="1:1" r="8">
+    <row r="8">
       <c r="A8" t="n">
         <v>8</v>
       </c>
     </row>
-    <row spans="1:1" r="9">
+    <row r="9">
       <c r="A9" t="n">
         <v>9</v>
       </c>
     </row>
-    <row spans="1:1" r="10">
+    <row r="10">
       <c r="A10" t="n">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins right="0.75" left="0.75" top="1" header="0.5" bottom="1" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>